--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Intern - Data Engineer - Summer 2026</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Acxiom</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Conway, AR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
+          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>AI Solutions Architect - Founding</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44885cba017a052</t>
+          <t>https://www.indeed.com/viewjob?jk=dad27261ac45880f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Solutions Architect - Founding</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad27261ac45880f</t>
+          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Backend Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=8de97150c606b641</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545ebacbf0ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Primary Data Architect - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=3c539bfe4180a449</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Primary Data Architect - Onsite Hybrid</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c539bfe4180a449</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>Tech Anchor</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FireMon</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>FireMon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, S3, IAM, RDS, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
@@ -1623,25 +1623,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b04fae137c25a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b04fae137c25a5f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,42 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ML Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7bd5ee5caf6d9e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Solutions Architect - Founding</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad27261ac45880f</t>
+          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Backend Engineer</t>
+          <t>AI Solutions Architect - Founding</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=dad27261ac45880f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
+          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de97150c606b641</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Primary Data Architect - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=9e9629f9b5b09640</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tech Anchor</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Tech Anchor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FireMon</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>FireMon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b04fae137c25a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,15 +1913,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,297 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b04fae137c25a5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AliCloud Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vaarida Technologies</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Devops Engineer-1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>UI/UX Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NIKSUN, Inc.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce76eb1050277d8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Primary Data Architect - Onsite Hybrid</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c539bfe4180a449</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
@@ -1051,29 +1051,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e9629f9b5b09640</t>
+          <t>https://www.indeed.com/viewjob?jk=3c539bfe4180a449</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Primary Data Architect - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=9e9629f9b5b09640</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>GAINSCO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=322e0a73c296fcdc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tech Anchor</t>
+          <t>IT System Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t xml:space="preserve">Tailored Edge Connections </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>North Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
+          <t>https://www.indeed.com/viewjob?jk=f856c765cc7cbf0f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Tech Anchor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=998975ecfa0fdb90</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FireMon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>FireMon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>IVN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, Scala, PostgreSQL, MySQL, NoSQL, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b04fae137c25a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>IT Data Analytics Engineer I, II, III or Senior</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Tri-State Generation &amp; Transmission</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bfdecf8fd48b4c94</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,15 +2088,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=1b04fae137c25a5f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,332 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Atmosera</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Devops Engineer-1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>UI/UX Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NIKSUN, Inc.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Solutions Architect - Founding</t>
+          <t>Intern - Data Engineer - Summer 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad27261ac45880f</t>
+          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
         </is>
       </c>
     </row>
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce76eb1050277d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Primary Data Architect - Onsite Hybrid</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c539bfe4180a449</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Primary Data Architect - Onsite Hybrid</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e9629f9b5b09640</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GAINSCO</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322e0a73c296fcdc</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT System Administrator</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tailored Edge Connections </t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North Aurora, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f856c765cc7cbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tech Anchor</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998975ecfa0fdb90</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FireMon</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IVN</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, PostgreSQL, MySQL, NoSQL, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT Data Analytics Engineer I, II, III or Senior</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tri-State Generation &amp; Transmission</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfdecf8fd48b4c94</t>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,497 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Klaviyo</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b04fae137c25a5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AliCloud Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Vaarida Technologies</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Cupertino, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Atmosera</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>ML Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>ML Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Trenton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Devops Engineer-1</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>UI/UX Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NIKSUN, Inc.</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Backend Engineer</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c44885cba017a052</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
+          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,46 +972,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
@@ -2072,6 +2072,76 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS, Databricks</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31364c52fe931267</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7bd5ee5caf6d9e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7bd5ee5caf6d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>Intern - Data Engineer - Summer 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
+          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Intern - Data Engineer - Summer 2026</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Acxiom</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Conway, AR, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
+          <t>https://www.indeed.com/viewjob?jk=c44885cba017a052</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44885cba017a052</t>
+          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Info Dhas Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=d89d6f2341484cb3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,45 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
         </is>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -1588,52 +1588,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Senior .NET / Azure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>FocusPointSAP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>Azure, Blob Storage, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa90f9fbfea59005</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Backend Engineer</t>
+          <t>AI Solutions Architect - Founding</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=dad27261ac45880f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
+          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce76eb1050277d8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,81 +1077,81 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Info Dhas Technologies</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89d6f2341484cb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Primary Data Architect - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=3c539bfe4180a449</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Primary Data Architect - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=9e9629f9b5b09640</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Tech Anchor</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior .NET / Azure Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FocusPointSAP</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa90f9fbfea59005</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=76bb466b98df6c5a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior .NET / Azure Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>FocusPointSAP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Blob Storage, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa90f9fbfea59005</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,147 +2036,742 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dulles, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d7c3843522209</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Application Developer, Consultant</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Blue Shield of California</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>El Dorado Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Georgetown, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cedar Park, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Analyst — AI-Driven Insights</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>David's Bridal</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Quality Engineer - San Jose, CA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Elekta</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8af71e9cc8f145e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Atmosera</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Devops Engineer-1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>ML Engineer</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>NYU Langone Health</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D65" t="n">
         <v>10.4</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,77 +591,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44885cba017a052</t>
+          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
+          <t>https://www.indeed.com/viewjob?jk=3832c96b614d30dc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Solutions Architect - Founding</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad27261ac45880f</t>
+          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Backend Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce76eb1050277d8</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Primary Data Architect - Onsite Hybrid</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c539bfe4180a449</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Primary Data Architect - Onsite Hybrid</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e9629f9b5b09640</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tech Anchor</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3343fdcb2c8d20e</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,137 +1686,137 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Tableau / Python Developer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bb466b98df6c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Dulles, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d7c3843522209</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior .NET / Azure Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FocusPointSAP</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa90f9fbfea59005</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dulles, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,112 +2096,112 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d7c3843522209</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,137 +2246,137 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,365 +2411,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Software Quality Engineer - San Jose, CA</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Elekta</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8af71e9cc8f145e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8588279f5d9918c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Atmosera</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Devops Engineer-1</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>ML Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>ML Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Trenton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
         </is>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Backend Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
@@ -923,35 +923,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dulles, VA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d7c3843522209</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,77 +2036,77 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,52 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Data Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Trenton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=37433ca9d18914f5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Technical Recruiter - AI Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Business Intelligence Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,15 +2376,260 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Atmosera</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AMETEK</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=37433ca9d18914f5</t>
         </is>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,35 +643,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
+          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>AI Mobile Developer / Co-Founder</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=85b154d3da56d200</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,54 +1161,54 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Technical Recruiter - AI Engineering</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Site Reliability Specialist III - MS SQL / Medical Imaging Systems</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intelerad</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f2b810200a5f10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Technical Recruiter - AI Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d4328781e85345ce</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
+          <t>https://www.indeed.com/viewjob?jk=080165bfea0f1891</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Corporate Data Engineering Specialist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>MCKIM &amp; CREED</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb2d6fbfda4c4a3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Business Intelligence Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,15 +2621,190 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Atmosera</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AMETEK</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=37433ca9d18914f5</t>
         </is>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Intern - Data Engineer - Summer 2026</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Acxiom</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Conway, AR, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
+          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Kalibri Labs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
+          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Mobile Developer / Co-Founder</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b154d3da56d200</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>AI Mobile Developer / Co-Founder</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=85b154d3da56d200</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,52 +1186,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Architect New</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=5097124275f0ddf7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site Reliability Specialist III - MS SQL / Medical Imaging Systems</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intelerad</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f2b810200a5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Technical Recruiter - AI Engineering</t>
+          <t>Site Reliability Specialist III - MS SQL / Medical Imaging Systems</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Intelerad</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f2b810200a5f10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Technical Recruiter - AI Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Aires</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=24a00011c009f4a8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Sr. Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
+          <t>https://www.indeed.com/viewjob?jk=d4328781e85345ce</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
+          <t>https://www.indeed.com/viewjob?jk=080165bfea0f1891</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Cloud/Software Engineer</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4328781e85345ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud/Software Engineer</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080165bfea0f1891</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Corporate Data Engineering Specialist</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MCKIM &amp; CREED</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb2d6fbfda4c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>API Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=5d9c6043097083ea</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
+          <t>Corporate Data Engineering Specialist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>MCKIM &amp; CREED</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb2d6fbfda4c4a3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Business Intelligence Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,15 +2796,120 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AMETEK</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=37433ca9d18914f5</t>
         </is>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
+          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kalibri Labs</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
+          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Kalibri Labs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,139 +626,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3832c96b614d30dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=3832c96b614d30dc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec427062b528812</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Mobile Developer / Co-Founder</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b154d3da56d200</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>AI Mobile Developer / Co-Founder</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=85b154d3da56d200</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,69 +1221,69 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Primary Data Architect - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=9e9629f9b5b09640</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect New</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5097124275f0ddf7</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Platform Infrastructure Engineer</t>
+          <t>Senior Data Analytics Engineer-Network Data Solutions</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
+          <t>https://www.indeed.com/viewjob?jk=a924d3cf5d03118f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Senior Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=a550b10b06b0495e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect New</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=5097124275f0ddf7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site Reliability Specialist III - MS SQL / Medical Imaging Systems</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intelerad</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f2b810200a5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technical Recruiter - AI Engineering</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aires</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a00011c009f4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=76bb466b98df6c5a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior .NET / Azure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>FocusPointSAP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>Azure, Blob Storage, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=fa90f9fbfea59005</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Site Reliability Specialist III - MS SQL / Medical Imaging Systems</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Intelerad</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f2b810200a5f10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Technical Recruiter - AI Engineering</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Cloud/Software Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4328781e85345ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud/Software Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080165bfea0f1891</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Product &amp; Audience Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
+          <t>https://www.indeed.com/viewjob?jk=d4328781e85345ce</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=080165bfea0f1891</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>API Architect (Onsite Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d9c6043097083ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Corporate Data Engineering Specialist</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MCKIM &amp; CREED</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb2d6fbfda4c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>API Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+          <t>https://www.indeed.com/viewjob?jk=5d9c6043097083ea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Corporate Data Engineering Specialist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>MCKIM &amp; CREED</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,15 +2901,295 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceb2d6fbfda4c4a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kash Tech</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Software Quality Engineer - San Jose, CA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Elekta</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8af71e9cc8f145e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Data Products</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AMETEK</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=37433ca9d18914f5</t>
         </is>

--- a/results/job_matches_2026-04-07.xlsx
+++ b/results/job_matches_2026-04-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
+          <t>https://www.indeed.com/viewjob?jk=650fc9401231f8ed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bdaecfc78dc80f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Senior Cloud Data Engineer – Multi‑Cloud Data Platforms</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, SQS, API Gateway, IAM, RDS, Azure, Data Factory, Synapse Analytics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3c59588504de4c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kalibri Labs</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
+          <t>https://www.indeed.com/viewjob?jk=86039d37dfab9cce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3832c96b614d30dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1520fe1ff993b458</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Systems Engineer, UDS Data Management - East</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AVN Corporation</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
+          <t>https://www.indeed.com/viewjob?jk=298a46f851ea7983</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Kalibri Labs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bba97db261f795c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>AVN Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=358914e57d4bcf85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
+          <t>https://www.indeed.com/viewjob?jk=12300277485ff36c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d695977c000b8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SR PLATFORM ENGINEER</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, SQL Server, MySQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
+          <t>https://www.indeed.com/viewjob?jk=98622b51534499ca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Principle Engineer, Software</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
+          <t>https://www.indeed.com/viewjob?jk=53c02ec3fd535863</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>SR PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4e87bc52fd3cc8c6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Principle Engineer, Software</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd418fd5773133</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development, Full Stack</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ee9996259cb8cd</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f52058e1d9e1079</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Senior Engineer, Software Development, Full Stack</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=feb13148be85e0d4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Applications Engineer 2026- US, UK</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
+          <t>https://www.indeed.com/viewjob?jk=60512437ff26ed1a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Mobile Developer / Co-Founder</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b154d3da56d200</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97ff98a1ad5a4b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Applications Engineer 2026- US, UK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mPower Software Services</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
+          <t>https://www.indeed.com/viewjob?jk=d0103d47ad6f0344</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Primary Data Architect - Onsite Hybrid</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>mPower Software Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, API Gateway, RDS, Scala, PostgreSQL, MongoDB, NoSQL, ETL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e9629f9b5b09640</t>
+          <t>https://www.indeed.com/viewjob?jk=378ab062dadbd830</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>ProfitSolv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
+          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c32b89e8538ed48</t>
+          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
         </is>
       </c>
     </row>
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8627a591401b5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Remote</t>
+          <t>Sr. ETL / Python Developer -Remote W2 role</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ProfitSolv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14597be3e3d5d6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. ETL / Python Developer -Remote W2 role</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, HBase, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b0c37814b35ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9babfbe8996948</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect New</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5097124275f0ddf7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d61b6eca49fa2fe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data Product</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b374f5fadc643</t>
+          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Results Generation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484671a3aa025748</t>
+          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Healthcare Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Results Generation</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9234cb66e9a7e360</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bda29f66d209a22</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=988a005246cd2194</t>
+          <t>https://www.indeed.com/viewjob?jk=b14638ca94876de4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Integrity Marketing Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c86386e71ccbf</t>
+          <t>https://www.indeed.com/viewjob?jk=4b528d73f04fa196</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cec9afb06f662f</t>
+          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,59 +1851,59 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46106626b8b759d3</t>
+          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Power BI</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5949fceede281d86</t>
+          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,15 +1913,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbde110bfeaa84c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524079054f8f7d18</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b62ca575690d77</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Tableau / Python Developer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bb466b98df6c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior .NET / Azure Engineer</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FocusPointSAP</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa90f9fbfea59005</t>
+          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Site Reliability Specialist III - MS SQL / Medical Imaging Systems</t>
+          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Intelerad</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f2b810200a5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technical Recruiter - AI Engineering</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f05de2af000d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=05b443f66d69fe26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ea863f4f9492f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1569defd5f50c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402ecae3cd52bd44</t>
+          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 (Databricks Administrator) - 26-03494</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4db862200c432b</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77818b9d286f244</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7bf203aa2f13913</t>
+          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc29a015a3c272e</t>
+          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6630164ce06047</t>
+          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer, Product &amp; Audience Technology</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad1dc41860f048c</t>
+          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Cloud/Software Engineer</t>
+          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4328781e85345ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud/Software Engineer</t>
+          <t>Data Engineer II, Data Products</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080165bfea0f1891</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,637 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddc21bb28ed1d22</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>nSCALE</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0779ded6bb449220</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>nSCALE</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Barstow, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efdadd031f04e3df</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Defense Unicorns</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd99e31ec539b3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Wichita, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4217e34fe61343</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc11b54459d6fd35</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d502aa87884ef6ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Consultant - Data &amp; AI (Microsoft Fabric) (Remote - US)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Atmosera</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9732977f36a28c</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Crescent Energy</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, GCP, Snowflake, SQL Server, Azure Cosmos DB, NoSQL, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16933d29b84666ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>API Architect (Onsite Hybrid)</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d9c6043097083ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Corporate Data Engineering Specialist</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>MCKIM &amp; CREED</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb2d6fbfda4c4a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Business Intelligence Architect</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Kash Tech</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Lake Mary, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d669d17cd5da84b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Backend)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be147597ae3a05</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Software Quality Engineer - San Jose, CA</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Elekta</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8af71e9cc8f145e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>AWS Full Stack React Developer (Onsite Hybrid)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e39392a5986a7e5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>ML Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f03a531b79570462</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Data Products</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d3e53b75102974</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>United States Cold Storage</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e69cc4d6409de612</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>AMETEK</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37433ca9d18914f5</t>
         </is>
       </c>
     </row>
